--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487444_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487444_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7987</v>
+        <v>6.0155</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9774</v>
+        <v>-0.6804</v>
       </c>
       <c r="F2" t="n">
-        <v>6.7761</v>
+        <v>6.6959</v>
       </c>
       <c r="G2" t="n">
         <v>4.785</v>
@@ -610,13 +610,13 @@
         <v>2.7419</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0646</v>
+        <v>0.1522</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4176</v>
+        <v>-0.1206</v>
       </c>
       <c r="U2" t="n">
-        <v>0.353</v>
+        <v>0.2728</v>
       </c>
       <c r="V2" t="n">
         <v>1.2742</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5149</v>
+        <v>4.5999</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3836</v>
+        <v>-0.5124</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8985</v>
+        <v>5.1123</v>
       </c>
       <c r="G3" t="n">
         <v>3.0608</v>
@@ -688,13 +688,13 @@
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1127</v>
+        <v>-0.0276</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0612</v>
+        <v>-0.19</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0515</v>
+        <v>0.1623</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4526</v>
+        <v>2.9089</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2677</v>
+        <v>2.336</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1849</v>
+        <v>0.5728</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6822</v>
+        <v>4.7432</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8476</v>
+        <v>0.0654</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8346</v>
+        <v>4.6778</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9146</v>
+        <v>4.2495</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6362</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2784</v>
+        <v>4.258</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.4937</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2114</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5562</v>
+        <v>0.4197</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7834</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4363</v>
+        <v>-0.4254</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9775</v>
+        <v>-0.1923</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4588</v>
+        <v>-0.233</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8825</v>
+        <v>0.9412</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6659</v>
+        <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6993</v>
+        <v>2.4679</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2602</v>
+        <v>1.3632</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4392</v>
+        <v>1.1047</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7432</v>
+        <v>4.6822</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0654</v>
+        <v>0.8476</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6778</v>
+        <v>3.8346</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2495</v>
+        <v>3.9146</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.6362</v>
       </c>
       <c r="L5" t="n">
-        <v>4.258</v>
+        <v>3.2784</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4937</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.2114</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4197</v>
+        <v>0.5562</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.3502</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6349</v>
+        <v>0.4515</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2682</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3667</v>
+        <v>0.3786</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9412</v>
+        <v>-1.8825</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>-0.6659</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5011</v>
+        <v>2.3098</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2272</v>
+        <v>1.0359</v>
       </c>
       <c r="F6" t="n">
         <v>1.2739</v>
@@ -922,10 +922,10 @@
         <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6197</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.904</v>
+        <v>-0.0953</v>
       </c>
       <c r="U6" t="n">
         <v>-0.7158</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.526</v>
+        <v>0.6343</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2167</v>
+        <v>1.3784</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6906</v>
+        <v>-0.7441</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6373</v>
@@ -1000,13 +1000,13 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2491</v>
+        <v>-0.1409</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1012</v>
+        <v>0.0606</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.148</v>
+        <v>-0.2014</v>
       </c>
       <c r="V7" t="n">
         <v>1.2166</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.466</v>
+        <v>-1.1798</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.3972</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7024</v>
+        <v>-0.7826</v>
       </c>
       <c r="G8" t="n">
         <v>0.6576</v>
@@ -1078,13 +1078,13 @@
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6939</v>
+        <v>-0.4077</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3982</v>
+        <v>-0.0318</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2958</v>
+        <v>-0.376</v>
       </c>
       <c r="V8" t="n">
         <v>0.3329</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9101</v>
+        <v>-2.5201</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.7249</v>
+        <v>-6.8537</v>
       </c>
       <c r="F9" t="n">
-        <v>4.8147</v>
+        <v>4.3336</v>
       </c>
       <c r="G9" t="n">
         <v>-3.6626</v>
@@ -1156,13 +1156,13 @@
         <v>2.546</v>
       </c>
       <c r="S9" t="n">
-        <v>0.832</v>
+        <v>0.222</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0159</v>
+        <v>-0.1129</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8161</v>
+        <v>0.335</v>
       </c>
       <c r="V9" t="n">
         <v>0.3329</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.0525</v>
+        <v>-6.6873</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.8742</v>
+        <v>-9.9367</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8217</v>
+        <v>3.2494</v>
       </c>
       <c r="G10" t="n">
         <v>-4.2224</v>
@@ -1234,13 +1234,13 @@
         <v>2.546</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1839</v>
+        <v>-0.8187</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3486</v>
+        <v>-0.4111</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8353</v>
+        <v>-0.4076</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2754</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.063999999999998</v>
+        <v>8.549100000000003</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.7519</v>
+        <v>-12.2669</v>
       </c>
       <c r="F11" t="n">
-        <v>20.816</v>
+        <v>20.8159</v>
       </c>
       <c r="G11" t="n">
         <v>10.8015</v>
@@ -1312,13 +1312,13 @@
         <v>14.6884</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.2905</v>
+        <v>-1.8056</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.5056</v>
+        <v>-1.0205</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7852000000000001</v>
+        <v>-0.7850999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>2.4906</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.2716</v>
+        <v>3.9383</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5125</v>
+        <v>1.3634</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7591</v>
+        <v>2.5748</v>
       </c>
       <c r="G12" t="n">
         <v>2.5991</v>
@@ -1390,13 +1390,13 @@
         <v>2.3502</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2601</v>
+        <v>1.9267</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5459</v>
+        <v>1.3968</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.5299</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>G. RODRIGUEZ LUQUE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2063</v>
+        <v>1.445</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2076</v>
+        <v>-2.1871</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4139</v>
+        <v>3.6321</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1856</v>
+        <v>-2.1329</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1689</v>
+        <v>-1.127</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3545</v>
+        <v>-1.0059</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0253</v>
+        <v>-2.238</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3084</v>
+        <v>-1.3374</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3337</v>
+        <v>-0.9006</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1603</v>
+        <v>0.1051</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1396</v>
+        <v>0.2104</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0208</v>
+        <v>-0.1053</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1958</v>
+        <v>1.7626</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1751</v>
+        <v>2.7419</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8248</v>
+        <v>0.5987</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7463</v>
+        <v>-0.1864</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0785</v>
+        <v>0.7852</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ LUQUE</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.383</v>
+        <v>1.2892</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.0058</v>
+        <v>-0.2076</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3888</v>
+        <v>1.4969</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.1329</v>
+        <v>0.1856</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.127</v>
+        <v>-1.1689</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0059</v>
+        <v>1.3545</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.238</v>
+        <v>0.0253</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.3374</v>
+        <v>-1.3084</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.9006</v>
+        <v>1.3337</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1051</v>
+        <v>0.1603</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2104</v>
+        <v>0.1396</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1053</v>
+        <v>0.0208</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7626</v>
+        <v>0.1958</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7419</v>
+        <v>1.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4633</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0051</v>
+        <v>0.7463</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.1614</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0348</v>
+        <v>0.5732</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4751</v>
+        <v>-0.9634</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5099</v>
+        <v>1.5366</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0835</v>
@@ -1624,13 +1624,13 @@
         <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7238</v>
+        <v>-0.1854</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5764</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1474</v>
+        <v>-0.1207</v>
       </c>
       <c r="V15" t="n">
         <v>0.2754</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3875</v>
+        <v>-0.3175</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3137</v>
+        <v>-0.6207</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.07389999999999999</v>
+        <v>0.3032</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4164</v>
@@ -1702,13 +1702,13 @@
         <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6579</v>
+        <v>0.728</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8475</v>
+        <v>0.5405</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1896</v>
+        <v>0.1875</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6083</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PRIETO LORIENTE</t>
+          <t>S. SHARASHIDZE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.512</v>
+        <v>-1.6158</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.6135</v>
+        <v>-3.3471</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1015</v>
+        <v>1.7312</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.7283</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3894</v>
+        <v>-1.4536</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.3389</v>
+        <v>1.4449</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.0437</v>
+        <v>-0.844</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.0779</v>
+        <v>-1.4599</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9659</v>
+        <v>0.6159</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3155</v>
+        <v>0.8353</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6885</v>
+        <v>0.0062</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.373</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1751</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1336</v>
+        <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4507</v>
+        <v>-0.1947</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3198</v>
+        <v>-0.487</v>
       </c>
       <c r="U17" t="n">
-        <v>0.869</v>
+        <v>0.2923</v>
       </c>
       <c r="V17" t="n">
-        <v>1.492</v>
+        <v>-1.2166</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7086</v>
+        <v>-0.0576</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2166</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>J. PRIETO LORIENTE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6727</v>
+        <v>-1.7025</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.2437</v>
+        <v>-4.5901</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5711</v>
+        <v>2.8876</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7512</v>
+        <v>-4.7283</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2614</v>
+        <v>-2.3894</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4898</v>
+        <v>-2.3389</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.974</v>
+        <v>-5.0437</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3322</v>
+        <v>-3.0779</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6418</v>
+        <v>-1.9659</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2228</v>
+        <v>0.3155</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0708</v>
+        <v>0.6885</v>
       </c>
       <c r="O18" t="n">
-        <v>0.152</v>
+        <v>-0.373</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9792</v>
+        <v>3.1336</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7236</v>
+        <v>0.3588</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3546</v>
+        <v>-0.2964</v>
       </c>
       <c r="U18" t="n">
-        <v>0.369</v>
+        <v>0.6552</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6659</v>
+        <v>1.492</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6659</v>
+        <v>2.7086</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. SHARASHIDZE</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7802</v>
+        <v>-3.4425</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.2681</v>
+        <v>-4.9601</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4879</v>
+        <v>1.5176</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-1.7512</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4536</v>
+        <v>-1.2614</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4449</v>
+        <v>-0.4898</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.844</v>
+        <v>-1.974</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4599</v>
+        <v>-1.3322</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6159</v>
+        <v>-0.6418</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8353</v>
+        <v>0.2228</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0062</v>
+        <v>0.0708</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.152</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7626</v>
+        <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3591</v>
+        <v>-0.0462</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.408</v>
+        <v>-0.3617</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0489</v>
+        <v>0.3155</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2166</v>
+        <v>-0.6659</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0576</v>
+        <v>-0.6659</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.8174</v>
+        <v>-7.1066</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.9049</v>
+        <v>-5.2119</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9125</v>
+        <v>-1.8947</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3788</v>
@@ -2014,13 +2014,13 @@
         <v>2.1543</v>
       </c>
       <c r="S20" t="n">
-        <v>0.308</v>
+        <v>0.0188</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0018</v>
+        <v>-0.3088</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3098</v>
+        <v>0.3276</v>
       </c>
       <c r="V20" t="n">
         <v>-2.9839</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.2741</v>
+        <v>-6.9392</v>
       </c>
       <c r="E21" t="n">
-        <v>-20.5199</v>
+        <v>-20.7246</v>
       </c>
       <c r="F21" t="n">
-        <v>13.2458</v>
+        <v>13.7853</v>
       </c>
       <c r="G21" t="n">
         <v>-10.7151</v>
@@ -2062,7 +2062,7 @@
         <v>-4.8257</v>
       </c>
       <c r="I21" t="n">
-        <v>-5.8895</v>
+        <v>-5.889500000000001</v>
       </c>
       <c r="J21" t="n">
         <v>-10.4914</v>
@@ -2092,13 +2092,13 @@
         <v>16.8429</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7775</v>
+        <v>4.1125</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1832</v>
+        <v>0.9785999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>2.5942</v>
+        <v>3.1339</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4907</v>
